--- a/Project Outputs for led_matrix_board/Assembly/BOM/Bill of Materials-led_matrix_board.xlsx
+++ b/Project Outputs for led_matrix_board/Assembly/BOM/Bill of Materials-led_matrix_board.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonathan.garnier\AppData\Local\Temp\Releases\Snapshot\1\Assembly\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B3BB19A-88EF-4F39-9872-4764CADAA502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91265FD4-E021-4E98-BAB4-D8616827C5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D4B53782-83D8-4331-824B-726A05CAD19E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{766A91FE-BFE6-4710-BDDC-5C577873EA4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-led_matrix_bo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="143">
   <si>
     <t>Designator</t>
   </si>
@@ -74,7 +74,55 @@
     <t>Supplier Unit Price 1</t>
   </si>
   <si>
-    <t>U4</t>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>HDR0162-1</t>
+  </si>
+  <si>
+    <t>PCB Receptacle, Board-to-Board, 2.54 mm, 2 Rows, 16 Contacts, Surface Mount</t>
+  </si>
+  <si>
+    <t>FP-SSM-108-L-DV-K-TR-MFG</t>
+  </si>
+  <si>
+    <t>Samtec</t>
+  </si>
+  <si>
+    <t>SSM-108-L-DV-K-TR</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>200-SSM108LDVKTR</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>ICT0297-2</t>
+  </si>
+  <si>
+    <t>Overvoltage Protection Controllers with Reverse Polarity Protection</t>
+  </si>
+  <si>
+    <t>MAX4866LEUT+T-Footprint-1</t>
+  </si>
+  <si>
+    <t>Analog Devices</t>
+  </si>
+  <si>
+    <t>MAX4866LEUT+T</t>
+  </si>
+  <si>
+    <t>Farnell</t>
+  </si>
+  <si>
+    <t>2799092</t>
+  </si>
+  <si>
+    <t>U5</t>
   </si>
   <si>
     <t>CMP-00035-1</t>
@@ -98,6 +146,51 @@
     <t>1428-1066-1-ND</t>
   </si>
   <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>SWH0003-1</t>
+  </si>
+  <si>
+    <t>SW, Tactile 15V@20mA, EVQ-PF, Through Hole, R/A, 7.5x7.1x5.85mm</t>
+  </si>
+  <si>
+    <t>EVQ-PF206K</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>Future Electronics</t>
+  </si>
+  <si>
+    <t>5121006</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>C1, C2</t>
+  </si>
+  <si>
+    <t>CAP0047-3</t>
+  </si>
+  <si>
+    <t>CAP CER 100UF 10V ±20% X5R 1210</t>
+  </si>
+  <si>
+    <t>CAPC3225X20N</t>
+  </si>
+  <si>
+    <t>Samsung Electro-Mechanics</t>
+  </si>
+  <si>
+    <t>CL32A107MPVNNNE</t>
+  </si>
+  <si>
+    <t>1276-3364-1-ND</t>
+  </si>
+  <si>
     <t>J1</t>
   </si>
   <si>
@@ -113,16 +206,13 @@
     <t>Same Sky</t>
   </si>
   <si>
-    <t>Farnell</t>
-  </si>
-  <si>
     <t>4814477</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>U1, U3</t>
+    <t>U2, U4</t>
   </si>
   <si>
     <t>ICT0294-1</t>
@@ -146,7 +236,7 @@
     <t/>
   </si>
   <si>
-    <t>H1, H2</t>
+    <t>H1</t>
   </si>
   <si>
     <t>JCK0020-1</t>
@@ -167,133 +257,106 @@
     <t>ED2600-ND</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>H3</t>
-  </si>
-  <si>
-    <t>HDR0159-1</t>
-  </si>
-  <si>
-    <t>Conn Shrouded Header (4 Sides) HDR 16 POS 2.54mm Solder ST Top Entry Thru-Hole</t>
-  </si>
-  <si>
-    <t>FP-SBH11-PBPC-D08-ST-BK-MFG</t>
-  </si>
-  <si>
-    <t>Sullins</t>
-  </si>
-  <si>
-    <t>SBH11-PBPC-D08-ST-BK</t>
-  </si>
-  <si>
-    <t>Future Electronics</t>
-  </si>
-  <si>
-    <t>1617539</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>SWH0003-1</t>
-  </si>
-  <si>
-    <t>SW, Tactile 15V@20mA, EVQ-PF, Through Hole, R/A, 7.5x7.1x5.85mm</t>
-  </si>
-  <si>
-    <t>EVQ-PF206K</t>
-  </si>
-  <si>
-    <t>Panasonic</t>
-  </si>
-  <si>
-    <t>2079503</t>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>TSR0028-1</t>
+  </si>
+  <si>
+    <t>Trans MOSFET N-CH 30V 5.7A 3-Pin SOT-23</t>
+  </si>
+  <si>
+    <t>FP-SOT23-IPC_C</t>
+  </si>
+  <si>
+    <t>Alpha &amp; Omega Semiconductor</t>
+  </si>
+  <si>
+    <t>AO3400A</t>
+  </si>
+  <si>
+    <t>785-1000-1-ND</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>DIO0053-6</t>
+  </si>
+  <si>
+    <t>LED GREEN 0402 SMD</t>
+  </si>
+  <si>
+    <t>LED_0402_GREEN</t>
+  </si>
+  <si>
+    <t>SunLED</t>
+  </si>
+  <si>
+    <t>XZVGR68W-3</t>
+  </si>
+  <si>
+    <t>1497-1386-1-ND</t>
+  </si>
+  <si>
+    <t>C3, C4, C5, C6</t>
+  </si>
+  <si>
+    <t>CAP0030-8</t>
+  </si>
+  <si>
+    <t>CAP CER 100NF 10V ±10% X7R 0603</t>
+  </si>
+  <si>
+    <t>0603_cap</t>
+  </si>
+  <si>
+    <t>KEMET</t>
+  </si>
+  <si>
+    <t>C0603C104K8RACTU</t>
+  </si>
+  <si>
+    <t>2112833</t>
+  </si>
+  <si>
+    <t>R2, R3, R4, R5</t>
+  </si>
+  <si>
+    <t>RES0003-8</t>
+  </si>
+  <si>
+    <t>RES SMD 0R OHM ±1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>0603_res</t>
+  </si>
+  <si>
+    <t>ERJ-3GEY0R00V</t>
+  </si>
+  <si>
+    <t>2059527</t>
   </si>
   <si>
     <t>D2</t>
   </si>
   <si>
-    <t>DIO0053-6</t>
-  </si>
-  <si>
-    <t>LED GREEN 0402 SMD</t>
-  </si>
-  <si>
-    <t>LED_0402_GREEN</t>
-  </si>
-  <si>
-    <t>SunLED</t>
-  </si>
-  <si>
-    <t>XZVGR68W-3</t>
-  </si>
-  <si>
-    <t>1497-1386-1-ND</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>DIO0043-4</t>
-  </si>
-  <si>
-    <t>TVS DIODE 3VWM ST020</t>
-  </si>
-  <si>
-    <t>0201_DIODE</t>
-  </si>
-  <si>
-    <t>STMicroelectronics</t>
-  </si>
-  <si>
-    <t>ESDALC6V1-1U2</t>
-  </si>
-  <si>
-    <t>1749278</t>
-  </si>
-  <si>
-    <t>C2, C3, C4, C5</t>
-  </si>
-  <si>
-    <t>CAP0030-8</t>
-  </si>
-  <si>
-    <t>CAP CER 100NF 10V ±10% X7R 0603</t>
-  </si>
-  <si>
-    <t>0603_cap</t>
-  </si>
-  <si>
-    <t>KEMET</t>
-  </si>
-  <si>
-    <t>C0603C104K8RACTU</t>
-  </si>
-  <si>
-    <t>2112833</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>CAP0197-9</t>
-  </si>
-  <si>
-    <t>CAP CER 10UF 25V ±20% X5R 0603</t>
-  </si>
-  <si>
-    <t>0603_cap_rnd</t>
-  </si>
-  <si>
-    <t>Murata</t>
-  </si>
-  <si>
-    <t>GRM188R61E106MA73J</t>
-  </si>
-  <si>
-    <t>1122095</t>
+    <t>DIO0005-3</t>
+  </si>
+  <si>
+    <t>Diodes, MBR120VLSFT1 Schottky 1A 20V, Vf=0.34V</t>
+  </si>
+  <si>
+    <t>SOD-123FL</t>
+  </si>
+  <si>
+    <t>onsemi</t>
+  </si>
+  <si>
+    <t>MBR120VLSFT1</t>
+  </si>
+  <si>
+    <t>Avnet</t>
   </si>
   <si>
     <t>MH1, MH2, MH3, MH4</t>
@@ -308,6 +371,24 @@
     <t>MH_600_320_NPTH</t>
   </si>
   <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>TSR0027-1</t>
+  </si>
+  <si>
+    <t>DMP3099L Series 30 V 65 mOhm P-Channel Enhancement Mode Mosfet - SOT-23-3</t>
+  </si>
+  <si>
+    <t>Diodes Inc.</t>
+  </si>
+  <si>
+    <t>DMP3099L-7</t>
+  </si>
+  <si>
+    <t>2050068</t>
+  </si>
+  <si>
     <t>R1</t>
   </si>
   <si>
@@ -329,7 +410,7 @@
     <t>2693604</t>
   </si>
   <si>
-    <t>R2</t>
+    <t>R6</t>
   </si>
   <si>
     <t>RES0219-8</t>
@@ -338,22 +419,31 @@
     <t>RES SMD 10K OHM ±1% 1/10W 0603</t>
   </si>
   <si>
-    <t>0603_res</t>
-  </si>
-  <si>
     <t>Royal Ohm</t>
   </si>
   <si>
     <t>0603WAF1002T5E</t>
   </si>
   <si>
-    <t>Mouser</t>
-  </si>
-  <si>
     <t>303-0603WAF1002T5E</t>
   </si>
   <si>
-    <t>R3</t>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>RES0224-8</t>
+  </si>
+  <si>
+    <t>RES SMD 100K OHM ±1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>0603WAF1003T5E</t>
+  </si>
+  <si>
+    <t>303-0603WAF1003T5E</t>
+  </si>
+  <si>
+    <t>R8</t>
   </si>
   <si>
     <t>RES0105-8</t>
@@ -368,22 +458,7 @@
     <t>1098364</t>
   </si>
   <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>RES0224-8</t>
-  </si>
-  <si>
-    <t>RES SMD 100K OHM ±1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>0603WAF1003T5E</t>
-  </si>
-  <si>
-    <t>303-0603WAF1003T5E</t>
-  </si>
-  <si>
-    <t>U2</t>
+    <t>U3</t>
   </si>
   <si>
     <t>MOD0041-1</t>
@@ -788,8 +863,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F62EB168-931F-4F3B-AC1E-993FB161A1C3}">
-  <dimension ref="A1:K17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A1266F8-1E6F-4D04-8C36-C3BA8554E894}">
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="5" width="18.81640625" customWidth="1"/>
@@ -863,7 +938,7 @@
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1">
-        <v>2.04</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -886,19 +961,17 @@
         <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="J3" s="1"/>
       <c r="K3" s="1">
-        <v>0.44174000000000002</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -909,7 +982,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>29</v>
@@ -924,16 +997,14 @@
         <v>32</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="J4" s="1"/>
       <c r="K4" s="1">
-        <v>0.376</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -944,7 +1015,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>37</v>
@@ -956,10 +1027,10 @@
         <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>41</v>
@@ -968,7 +1039,7 @@
         <v>42</v>
       </c>
       <c r="K5" s="1">
-        <v>0.32169999999999999</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -979,7 +1050,7 @@
         <v>44</v>
       </c>
       <c r="C6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>45</v>
@@ -994,49 +1065,51 @@
         <v>48</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="K6" s="1">
-        <v>0.215</v>
+        <v>0.50700000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="K7" s="1">
-        <v>0.19183</v>
+        <v>0.45250000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -1047,7 +1120,7 @@
         <v>58</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>59</v>
@@ -1062,298 +1135,432 @@
         <v>62</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="K8" s="1">
-        <v>0.16439999999999999</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K9" s="1">
-        <v>0.10915</v>
+        <v>0.32169999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="J10" s="1"/>
       <c r="K10" s="1">
-        <v>3.8100000000000002E-2</v>
+        <v>0.1787</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1">
+        <v>0.14499999999999999</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+        <v>89</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3.9019999999999999E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1">
+        <v>1.149E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C15" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
+        <v>119</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
